--- a/daily_matches/job_matches_2026-06-24.xlsx
+++ b/daily_matches/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,200 +468,200 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer - Archimedes</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4751e9b6daa317e5</t>
+          <t>https://www.indeed.com/viewjob?jk=06ac01a3b37b1411</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Engineer, Data - Archimedes</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Common Sense Media</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>24.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fb1410c88e482e8</t>
+          <t>https://www.indeed.com/viewjob?jk=00efdae7133cac10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Terraform, Git, PostgreSQL, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e26fb0df2e45c4d</t>
+          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Engineer, Development Operations - Archimedes</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539a2819d0a1864f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ML Ops and Model accuracy Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Flexday</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, MLflow, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Synapse, Docker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b36b244637e89a0</t>
+          <t>https://www.indeed.com/viewjob?jk=95cbc1c146d97972</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior SDET (Java)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Flexday</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Synapse, Docker</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,112 +671,462 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9274aa15d195b18e</t>
+          <t>https://www.indeed.com/viewjob?jk=8414509fa2b039f4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Manufacturing Execution Systems (MES)</t>
+          <t>Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bright Machines</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Florence, KY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, FastAPI, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d8690fc87f9ed3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior SDET (Java)</t>
+          <t>Sr. Engineer, Cloud - Archimedes</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4a285b5608e1651</t>
+          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Generative AI Scientist II - (Model Risk &amp; Validation)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Litera</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=669db71a6daa2365</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Generative AI Scientist - (Model Risk &amp; Validation)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cotiviti</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ea23170869cc1bb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sr. Architect, Enterprise - Archimedes</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Data Lake, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Engineer, Development Operations - Archimedes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Synapse, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr. Engineer, Software - Archimedes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, AKS, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Engineer, Data Integration - Archimedes</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Navitus Health Solutions / Lumicera Health Services</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI/ML Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Manifold Bio</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, EC2, Kubernetes, CI/CD, Git, Snowflake, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=79a02bc63cbf844b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EchoStar</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Cheyenne, WY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=675da49c9b2f2e0f</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c6038ec3b3466e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ada9a80fb5db3e85</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1bbb343d60ee67a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Python Developer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Infyni</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Southfield, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13cc0efa04c752d5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-24.xlsx
+++ b/daily_matches/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,152 +468,152 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer - Archimedes</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06ac01a3b37b1411</t>
+          <t>https://www.indeed.com/viewjob?jk=513b06edfb3e0c5a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Data - Archimedes</t>
+          <t>AI/ML Engineer (Senior Associate) - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24.4</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Redshift, Synapse, Data Lake, MLflow, Apache Airflow, CI/CD</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00efdae7133cac10</t>
+          <t>https://www.indeed.com/viewjob?jk=56abd1ac683b8c11</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Development Operations - Archimedes</t>
+          <t>Full Stack Software Engineer - AI Applications</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD</t>
+          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=849fb6429e007fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d497fc5311c699a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer, Development Operations - Archimedes</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Vectra AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, Docker, Kubernetes, AKS, CI/CD, GitHub Actions</t>
+          <t>Data Scientist, FastAPI, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea98351890cb41a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e361ec91914e9985</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/ML Engineer — GTM Automation - Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Flexday</t>
+          <t>Aptasentry</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Synapse, Docker</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cbc1c146d97972</t>
+          <t>https://www.indeed.com/viewjob?jk=e7cf1eac3e10df55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Developer (Angular/Java)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Flexday</t>
+          <t>S2Alliance Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Gemini, Copilot, Pinecone, Prompt Engineering, Synapse, Docker</t>
+          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,462 +671,112 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8414509fa2b039f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6989bdbea1dddcfd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Engineer, Cloud - Archimedes</t>
+          <t>Sr. AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>Generative AI, RAG, Prompt Engineering, XGBoost, MLflow, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2f878a6cd6c513</t>
+          <t>https://www.indeed.com/viewjob?jk=5b47d0c2cfc2bb5c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud - Archimedes</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
+          <t>Kinsale Management Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Data Lake, MLflow, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>RAG, Copilot, Docker, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7995f8317591305</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9ff4676bcc42ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Generative AI Scientist II - (Model Risk &amp; Validation)</t>
+          <t>Software Engineer II - Localization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>TORC Robotics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
+          <t>RAG, PyTorch, Docker, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=669db71a6daa2365</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Generative AI Scientist - (Model Risk &amp; Validation)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, TensorFlow, PyTorch, Keras, NLTK</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea23170869cc1bb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sr. Architect, Enterprise - Archimedes</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, Data Lake, MLflow, Kubernetes, AKS, CI/CD, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=096a8034fe908404</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Engineer, Development Operations - Archimedes</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Synapse, Data Lake, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8da20c80b6159763</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr. Engineer, Software - Archimedes</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Data Lake, AKS, CI/CD, GitHub Actions, Git, Databricks, PostgreSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=084467bb5807c6b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Engineer, Data Integration - Archimedes</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Navitus Health Solutions / Lumicera Health Services</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Kafka, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a819a6db45f8192</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>AI/ML Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Manifold Bio</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, EC2, Kubernetes, CI/CD, Git, Snowflake, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79a02bc63cbf844b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Database Administrator</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Cheyenne, WY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Kubernetes, PostgreSQL, MySQL, Cassandra, NoSQL, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c6038ec3b3466e1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Engineering</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GitHub</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ada9a80fb5db3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>State Farm</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Databricks, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1bbb343d60ee67a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Python Developer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Infyni</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Southfield, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13cc0efa04c752d5</t>
+          <t>https://www.indeed.com/viewjob?jk=81def5e54cf5cbd9</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-24.xlsx
+++ b/daily_matches/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer-Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, Kafka, MongoDB, NoSQL</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, S3, Data Lake, Git, Databricks, Kafka, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=513b06edfb3e0c5a</t>
+          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer (Senior Associate) - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>iEnjoy Home</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, FastAPI, Docker, CI/CD</t>
+          <t>RAG, Gemini, BigQuery, CI/CD, GitHub Actions, Git, BigQuery, PostgreSQL, MySQL, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56abd1ac683b8c11</t>
+          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - AI Applications</t>
+          <t>Azure Senior Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, BigQuery, AKS, CI/CD, Terraform, Git, BigQuery, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Azure ML, Synapse, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d497fc5311c699a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Software Development Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vectra AI</t>
+          <t>PitchBook</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, FastAPI, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e361ec91914e9985</t>
+          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Engineer — GTM Automation - Intern</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aptasentry</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, FastAPI, Docker, Git, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cf1eac3e10df55</t>
+          <t>https://www.indeed.com/viewjob?jk=eee2438c93d66aa3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Developer (Angular/Java)</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S2Alliance Inc</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989bdbea1dddcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee13b6718e1d716</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wellington Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, XGBoost, MLflow, CI/CD, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b47d0c2cfc2bb5c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Analytics and AI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kinsale Management Inc</t>
+          <t>Rochester Electronics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Newburyport, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, Synapse, CI/CD, Snowflake, BigQuery, Redshift, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,707 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9ff4676bcc42ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II - Localization</t>
+          <t>SDE I- Adobe Exp Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TORC Robotics</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Generative AI, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>National Grid</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GCP Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>HCLTech</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Glue, BigQuery, Synapse, Data Lake, Snowflake, Databricks, BigQuery, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Scientist (Remote)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Alignment Healthcare</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Orange, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb60f1b978e81e25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Remote Senior Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Quintile Advisory</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f10bb5e3b3aff3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Trellix</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Frisco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327727953a748886</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Minerva</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Glue, Redshift, Data Lake, Snowflake, Redshift, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3db7ac8b225e8c2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Voice Backend Software Engineer (Node.js and Java) | Remote | US</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sutherland</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5021c4813eb82bea</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Video Streaming DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NBCUniversal</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0bdf14721c9859d</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cayuse Holdings</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8341ee08f1009400</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Orange Apron Media (Remote)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=191b283f6fb5e4be</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Exegy</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Gemini, S3, EC2, Docker, CI/CD, Jenkins, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55ec4db14d7990ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Engineer II, Software</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6938c4e3f8f25679</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27ccece82d65d0c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, Docker, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81def5e54cf5cbd9</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d136b839936bfe00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=562b3643a2e57a11</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51ec1644bdc7de0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ca55c6b918dc6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Machine Learning Operations Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CliftonLarsonAllen</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49df70903d8789c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>engineer sr - Corporate and Manufacturing Networking – Global Technology</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Starbucks</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c92a570620a173e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-24.xlsx
+++ b/daily_matches/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer-Adobe Exp Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>NinjaTrader</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, S3, Data Lake, Git, Databricks, Kafka, Hadoop</t>
+          <t>RAG, S3, Glue, Athena, BigQuery, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b2fc4d359a22654</t>
+          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>iEnjoy Home</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Gemini, BigQuery, CI/CD, GitHub Actions, Git, BigQuery, PostgreSQL, MySQL, Power BI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105d305fcaa2ff1b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec7670555c78b7db</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, Azure ML, Synapse, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d5a70d178b56c84</t>
+          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer, Platform Engineering</t>
+          <t>Sr. Engineer, AI &amp; ML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PitchBook</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, MySQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e6071131867132b</t>
+          <t>https://www.indeed.com/viewjob?jk=226ca382f5d1c3cd</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee2438c93d66aa3</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8a2308df02e747</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI &amp; ML</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, MongoDB, Cassandra, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee13b6718e1d716</t>
+          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wellington Management</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>S3, Glue, Redshift, Data Lake, Apache Airflow, CI/CD, Databricks, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e2eb7f5e0e5869a</t>
+          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics and AI Developer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rochester Electronics</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Newburyport, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Synapse, CI/CD, Snowflake, BigQuery, Redshift, Tableau</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, AWS SageMaker, Azure ML</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c295c697727454</t>
+          <t>https://www.indeed.com/viewjob?jk=07e8015eb99197db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SDE I- Adobe Exp Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, SQL, R</t>
+          <t>RAG, Cortex, Data Lake, Apache Airflow, CI/CD, Terraform, Snowflake, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5cf1edb1b7ec954</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
         </is>
       </c>
     </row>
@@ -788,20 +788,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>National Grid</t>
+          <t>Watchguard Technologies</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Snowflake, Databricks, PySpark, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Cortex, Data Lake, Apache Airflow, CI/CD, Terraform, Snowflake, PySpark, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=342d1ce362be0803</t>
+          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Senior Data Architect</t>
+          <t>Applied Data Scientist - AI Enablement (Transportation)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Glue, BigQuery, Synapse, Data Lake, Snowflake, Databricks, BigQuery, R</t>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29c5430e519b8187</t>
+          <t>https://www.indeed.com/viewjob?jk=e20d4da232c4244b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist (Remote)</t>
+          <t>System Analyst Artificial Intelligence/Machine Learning</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>DANE LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Woodbridge, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, NoSQL, Python, SQL, R</t>
+          <t>TensorFlow, PyTorch, NLTK, Git, PostgreSQL, MySQL, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb60f1b978e81e25</t>
+          <t>https://www.indeed.com/viewjob?jk=237f8c6bbb650cab</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Remote Senior Automation Engineer</t>
+          <t>Full Stack Software Engineer - Ford Pro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quintile Advisory</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f10bb5e3b3aff3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Business Intelligence Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Trellix</t>
+          <t>Crane Worldwide Logistics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=327727953a748886</t>
+          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Limited Tenure - Hybrid</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Minerva</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Glue, Redshift, Data Lake, Snowflake, Redshift, MySQL, Python, SQL</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db7ac8b225e8c2d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Voice Backend Software Engineer (Node.js and Java) | Remote | US</t>
+          <t>AI Engineer, Brooklyn Direct Indexing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sutherland</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Copilot, S3, FastAPI, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5021c4813eb82bea</t>
+          <t>https://www.indeed.com/viewjob?jk=8c82d65699484bcb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Video Streaming DevOps Engineer</t>
+          <t>Engineer II, Software</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NBCUniversal</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0bdf14721c9859d</t>
+          <t>https://www.indeed.com/viewjob?jk=907ff64b5ace226a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Python, R, Java, Scala</t>
+          <t>RAG, S3, Glue, Redshift, Git, Snowflake, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8341ee08f1009400</t>
+          <t>https://www.indeed.com/viewjob?jk=55f2a46d6315cf2e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Orange Apron Media (Remote)</t>
+          <t>Senior Infrastructure Software Engineer, Deep Learning Libraries</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Git, Python, R, Java, Scala, Optimization</t>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=191b283f6fb5e4be</t>
+          <t>https://www.indeed.com/viewjob?jk=cde9a70527386d5b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Exegy</t>
+          <t>Quantifind</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gemini, S3, EC2, Docker, CI/CD, Jenkins, Git, Python, R, Scala</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55ec4db14d7990ee</t>
+          <t>https://www.indeed.com/viewjob?jk=efec5f4d3211f2dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer II, Software</t>
+          <t>Sr. Analyst, Retail Data Strategy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6938c4e3f8f25679</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc54b38771ba683</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI / ML Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, Python, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27ccece82d65d0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=71f28ac3a6a5dff7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d136b839936bfe00</t>
+          <t>https://www.indeed.com/viewjob?jk=1d2e33b0bf6f410c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Product Engineer II - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Kubernetes, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562b3643a2e57a11</t>
+          <t>https://www.indeed.com/viewjob?jk=4172ffc795a8a9ef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst, Search and Recommendations</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ec1644bdc7de0b</t>
+          <t>https://www.indeed.com/viewjob?jk=b11f8b92c3787212</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Infrastructure Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,77 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca55c6b918dc6a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Machine Learning Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>CliftonLarsonAllen</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Jenkins, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=49df70903d8789c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>engineer sr - Corporate and Manufacturing Networking – Global Technology</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Starbucks</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c92a570620a173e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfdc39338a402033</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-24.xlsx
+++ b/daily_matches/job_matches_2026-06-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NinjaTrader</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, BigQuery, Data Lake, Kinesis, Kubernetes, CI/CD, Terraform</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c77bde68b2f181a8</t>
+          <t>https://www.indeed.com/viewjob?jk=729ea3d76920022c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, Hugging Face, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec7670555c78b7db</t>
+          <t>https://www.indeed.com/viewjob?jk=bda8a2212b29d396</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Application Engineer (HYBRID TO MA)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>The Hanover Insurance Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c8f68d352133895</t>
+          <t>https://www.indeed.com/viewjob?jk=2407067c993e95a7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI &amp; ML</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Databricks, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=226ca382f5d1c3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=04f1431d2e065885</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Engineer, AI &amp; ML</t>
+          <t>Data Workflow Engineer – AI &amp; Automation Focus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Azure ML, MLflow, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8a2308df02e747</t>
+          <t>https://www.indeed.com/viewjob?jk=461aa75a8d591411</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>Software Engineer, AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>DIVERGENT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Terraform, Git, Kafka, MongoDB, Cassandra, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, PyTorch, Docker, Kubernetes, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7efd71fe94ac695</t>
+          <t>https://www.indeed.com/viewjob?jk=bec27ff492f3ea56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Flashpoint</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Data Lake, Apache Airflow, CI/CD, Databricks, Redshift, Python, SQL</t>
+          <t>RAG, Gemini, Prompt Engineering, BigQuery, Dataflow, Terraform, BigQuery, Kafka, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97eae083068a3900</t>
+          <t>https://www.indeed.com/viewjob?jk=56a20902c87e77db</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Software Engineer II, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, PyTorch, AWS SageMaker, Azure ML</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e8015eb99197db</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1cba0795fa5f08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Data Lake, Apache Airflow, CI/CD, Terraform, Snowflake, PySpark, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9c70888519239b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e99b981a057dcf0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Watchguard Technologies</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Data Lake, Apache Airflow, CI/CD, Terraform, Snowflake, PySpark, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0779aea1cfbfb91d</t>
+          <t>https://www.indeed.com/viewjob?jk=72c35dad8cc6a352</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Applied Data Scientist - AI Enablement (Transportation)</t>
+          <t>Software Engineer II, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Copilot, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e20d4da232c4244b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d3e662d32c8477</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>System Analyst Artificial Intelligence/Machine Learning</t>
+          <t>Software Engineer II, Site Reliability Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DANE LLC</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Woodbridge, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, NLTK, Git, PostgreSQL, MySQL, Power BI, Matplotlib, Seaborn, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=237f8c6bbb650cab</t>
+          <t>https://www.indeed.com/viewjob?jk=02f85d363dff4877</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer - Ford Pro</t>
+          <t>AI Identity Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b141aab9409e42fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db7aabfe4602bdba</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II</t>
+          <t>AI Identity Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crane Worldwide Logistics</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803ae398014df5d9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b1760c07d1997a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Limited Tenure - Hybrid</t>
+          <t>Data &amp; Analytics Customer Engineer (SQL, AzureSQL, Power BI &amp; MS Fabric)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>JDA TSG</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, Synapse, Databricks, PostgreSQL, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e43e4fbeec2a74d</t>
+          <t>https://www.indeed.com/viewjob?jk=4eefcc29cc0f34a1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Engineer, Brooklyn Direct Indexing</t>
+          <t>AI Identity Security Engineer (SailPoint)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, FastAPI, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c82d65699484bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=436cf493867e94e5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer II, Software</t>
+          <t>Senior Hr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Dollar Tree</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Reseda, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Dataflow, PySpark, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907ff64b5ace226a</t>
+          <t>https://www.indeed.com/viewjob?jk=54e8257ac428173c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Vivian Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Git, Snowflake, Redshift, Python, SQL, R</t>
+          <t>Redshift, BigQuery, Terraform, Snowflake, BigQuery, Redshift, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f2a46d6315cf2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac65c61b2da2ea9a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Software Engineer, Deep Learning Libraries</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, Terraform, MySQL, Cassandra, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cde9a70527386d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe70c0ae09b9a043</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Forward Deployed Engineer</t>
+          <t>Applied AI ML, Senior Associate - Sales Science</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quantifind</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efec5f4d3211f2dc</t>
+          <t>https://www.indeed.com/viewjob?jk=2c33cf5648a0455b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Retail Data Strategy</t>
+          <t>Forward Deployed Analytics Engineer &amp; AI Specialist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Tableau, Power BI, SQL, R</t>
+          <t>RAG, Copilot, Cortex, CI/CD, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc54b38771ba683</t>
+          <t>https://www.indeed.com/viewjob?jk=a20265e12f4d3969</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SRE Engineer / Site Reliability Engineer Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, SQL, R, Java</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f28ac3a6a5dff7</t>
+          <t>https://www.indeed.com/viewjob?jk=5727c307ab31a8b6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - Fabric (100% Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>ClearCaptions, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, Dataflow, CI/CD, Git, PySpark, Power BI, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2e33b0bf6f410c</t>
+          <t>https://www.indeed.com/viewjob?jk=50b81073918a7625</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Product Engineer II - Cloud Infrastructure</t>
+          <t>Sr. Backend Engineer, Infrastructure team</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Pinwheel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4172ffc795a8a9ef</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac41e6824b8624a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Analyst, Search and Recommendations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>EWC Corporate LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+          <t>RAG, S3, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11f8b92c3787212</t>
+          <t>https://www.indeed.com/viewjob?jk=0244beb9aaca2837</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Infrastructure Administrator</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Avery Dennison</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Mentor, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Git, Tableau, Matplotlib, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,42 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfdc39338a402033</t>
+          <t>https://www.indeed.com/viewjob?jk=afb91044f60b446f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Associate Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d9fed1c77edefdb</t>
         </is>
       </c>
     </row>
